--- a/input-rsp/RSP_Outbound_Jan26.xlsx
+++ b/input-rsp/RSP_Outbound_Jan26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DQ3"/>
+  <dimension ref="A1:DQ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,6 +1108,96 @@
         </is>
       </c>
       <c r="BB3" t="inlineStr">
+        <is>
+          <t>Self-Employed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>901OBJan26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ATH160001</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Piti</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2020000000901</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Self-Employed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>902OBJan26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ATH160001</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Somchai</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>2020000000902</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>Self-Employed</t>
         </is>
